--- a/CardData/AttackCard.xlsx
+++ b/CardData/AttackCard.xlsx
@@ -56,7 +56,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>(array#sep=_),int</t>
+    <t xml:space="preserve">(array#sep=,), (array#sep=_),int</t>
   </si>
   <si>
     <t>string</t>
@@ -106,7 +106,7 @@
 将一张直击III加入手牌。</t>
   </si>
   <si>
-    <t>4_0_1_0,5_0_2_1_0</t>
+    <t>4_1_0_0,5_0_2_1_0</t>
   </si>
   <si>
     <t>w_0</t>
@@ -622,10 +622,10 @@
         <v>1</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>53</v>
@@ -657,7 +657,7 @@
         <v>56</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2</v>
